--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/140.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/140.xlsx
@@ -426,13 +426,13 @@
         <v>-1.598295716330578</v>
       </c>
       <c r="E2">
-        <v>-20.07879420207295</v>
+        <v>-20.01355971179387</v>
       </c>
       <c r="F2">
-        <v>1.395718574831588</v>
+        <v>-0.3320404518834532</v>
       </c>
       <c r="G2">
-        <v>-10.72154426815585</v>
+        <v>-10.76995269436427</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.606365844604109</v>
       </c>
       <c r="E3">
-        <v>-21.7084021892299</v>
+        <v>-20.85217614250325</v>
       </c>
       <c r="F3">
-        <v>0.7639161297771824</v>
+        <v>0.4066553511956031</v>
       </c>
       <c r="G3">
-        <v>-11.07307711123237</v>
+        <v>-10.58937532323074</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.686783667344527</v>
       </c>
       <c r="E4">
-        <v>-22.92746939013887</v>
+        <v>-20.92253569555717</v>
       </c>
       <c r="F4">
-        <v>0.8424138816012691</v>
+        <v>0.140128967712265</v>
       </c>
       <c r="G4">
-        <v>-11.02779244092721</v>
+        <v>-10.41992364017223</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.840667765372188</v>
       </c>
       <c r="E5">
-        <v>-22.45014081257633</v>
+        <v>-21.73154803594317</v>
       </c>
       <c r="F5">
-        <v>1.546844267063524</v>
+        <v>0.1413516379987971</v>
       </c>
       <c r="G5">
-        <v>-11.29276604708537</v>
+        <v>-11.05246658805782</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.066059662958754</v>
       </c>
       <c r="E6">
-        <v>-23.60777786477976</v>
+        <v>-23.00226457288771</v>
       </c>
       <c r="F6">
-        <v>1.681611359824975</v>
+        <v>0.2753897674457851</v>
       </c>
       <c r="G6">
-        <v>-10.96495965085289</v>
+        <v>-11.54739718854583</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.355380779694257</v>
       </c>
       <c r="E7">
-        <v>-24.83729039217068</v>
+        <v>-22.98147775020695</v>
       </c>
       <c r="F7">
-        <v>0.2030368450156651</v>
+        <v>0.273952550001928</v>
       </c>
       <c r="G7">
-        <v>-11.30312417625061</v>
+        <v>-11.57141603878407</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.698557434290789</v>
       </c>
       <c r="E8">
-        <v>-26.0733940659341</v>
+        <v>-24.05009902408533</v>
       </c>
       <c r="F8">
-        <v>2.194934071991773</v>
+        <v>0.512826372845013</v>
       </c>
       <c r="G8">
-        <v>-10.29566002986902</v>
+        <v>-11.37952108984806</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.083575515922262</v>
       </c>
       <c r="E9">
-        <v>-26.21290458754642</v>
+        <v>-24.43165454849733</v>
       </c>
       <c r="F9">
-        <v>1.689172697477729</v>
+        <v>0.8670147367296088</v>
       </c>
       <c r="G9">
-        <v>-11.00981876978969</v>
+        <v>-11.39874008615554</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.494819799881691</v>
       </c>
       <c r="E10">
-        <v>-27.24676763584731</v>
+        <v>-25.27485612450932</v>
       </c>
       <c r="F10">
-        <v>2.011439095128043</v>
+        <v>1.147219951135375</v>
       </c>
       <c r="G10">
-        <v>-11.73702862192134</v>
+        <v>-11.44645666504732</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.908188799130463</v>
       </c>
       <c r="E11">
-        <v>-28.34452368716937</v>
+        <v>-25.98663763456976</v>
       </c>
       <c r="F11">
-        <v>2.289762258794649</v>
+        <v>1.394678145373671</v>
       </c>
       <c r="G11">
-        <v>-9.626945215673555</v>
+        <v>-11.30229004335375</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.306124301753237</v>
       </c>
       <c r="E12">
-        <v>-27.9816410008738</v>
+        <v>-25.85381378319041</v>
       </c>
       <c r="F12">
-        <v>3.29751924960961</v>
+        <v>1.59726699087193</v>
       </c>
       <c r="G12">
-        <v>-9.537216534821582</v>
+        <v>-11.34146687668799</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.67146698277449</v>
       </c>
       <c r="E13">
-        <v>-30.87428208402435</v>
+        <v>-28.14842150804494</v>
       </c>
       <c r="F13">
-        <v>2.904405901467466</v>
+        <v>2.061921461389451</v>
       </c>
       <c r="G13">
-        <v>-11.41371792787476</v>
+        <v>-11.28088193770662</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.992070061312748</v>
       </c>
       <c r="E14">
-        <v>-28.97062237099293</v>
+        <v>-28.08940437511912</v>
       </c>
       <c r="F14">
-        <v>3.207979360306206</v>
+        <v>2.439769655032806</v>
       </c>
       <c r="G14">
-        <v>-9.621804659573652</v>
+        <v>-11.24643316282688</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.25855469880671</v>
       </c>
       <c r="E15">
-        <v>-31.48081706590231</v>
+        <v>-30.7316794965807</v>
       </c>
       <c r="F15">
-        <v>3.512949446586067</v>
+        <v>2.620655274577717</v>
       </c>
       <c r="G15">
-        <v>-11.14411547155656</v>
+        <v>-11.11346141394</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.473407503655859</v>
       </c>
       <c r="E16">
-        <v>-32.18453303956993</v>
+        <v>-29.44007438327794</v>
       </c>
       <c r="F16">
-        <v>4.307797790798693</v>
+        <v>2.728795325543582</v>
       </c>
       <c r="G16">
-        <v>-9.185571429727647</v>
+        <v>-10.02525476958905</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.643754794053006</v>
       </c>
       <c r="E17">
-        <v>-31.87352396272148</v>
+        <v>-31.41900482175489</v>
       </c>
       <c r="F17">
-        <v>4.399332388808038</v>
+        <v>3.550744537706197</v>
       </c>
       <c r="G17">
-        <v>-9.176394662489884</v>
+        <v>-10.0800294964829</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.777545467981231</v>
       </c>
       <c r="E18">
-        <v>-32.87359856028923</v>
+        <v>-31.91607776595567</v>
       </c>
       <c r="F18">
-        <v>4.65416305293125</v>
+        <v>3.971672806499543</v>
       </c>
       <c r="G18">
-        <v>-8.924956461664355</v>
+        <v>-9.186214978269355</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.88915751809057</v>
       </c>
       <c r="E19">
-        <v>-34.45266819544</v>
+        <v>-32.90150191057509</v>
       </c>
       <c r="F19">
-        <v>4.738669781895244</v>
+        <v>3.978553226147196</v>
       </c>
       <c r="G19">
-        <v>-9.208489851120735</v>
+        <v>-9.572955017529331</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.992779075989911</v>
       </c>
       <c r="E20">
-        <v>-37.32621073631334</v>
+        <v>-32.72984968651993</v>
       </c>
       <c r="F20">
-        <v>5.420437691951711</v>
+        <v>4.54477548065677</v>
       </c>
       <c r="G20">
-        <v>-7.942278724430791</v>
+        <v>-8.660908364463747</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.102025908413573</v>
       </c>
       <c r="E21">
-        <v>-36.29802305128782</v>
+        <v>-34.05640199651546</v>
       </c>
       <c r="F21">
-        <v>5.550418477859786</v>
+        <v>4.858975236538623</v>
       </c>
       <c r="G21">
-        <v>-8.706421474920624</v>
+        <v>-8.668739292864791</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.221035233049824</v>
       </c>
       <c r="E22">
-        <v>-37.46221179435617</v>
+        <v>-35.5050504130383</v>
       </c>
       <c r="F22">
-        <v>5.378678034441782</v>
+        <v>5.086461492695422</v>
       </c>
       <c r="G22">
-        <v>-9.197349803950454</v>
+        <v>-8.831024482020689</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.357420679053861</v>
       </c>
       <c r="E23">
-        <v>-38.43838881396086</v>
+        <v>-35.40484796000983</v>
       </c>
       <c r="F23">
-        <v>5.910380562541895</v>
+        <v>5.417689168909222</v>
       </c>
       <c r="G23">
-        <v>-6.911140346096983</v>
+        <v>-8.336973702459888</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.511274125649533</v>
       </c>
       <c r="E24">
-        <v>-38.46469525449232</v>
+        <v>-36.91056772995281</v>
       </c>
       <c r="F24">
-        <v>7.140610529991913</v>
+        <v>5.690682616706216</v>
       </c>
       <c r="G24">
-        <v>-7.581046965198288</v>
+        <v>-6.607220957500894</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.678893026737854</v>
       </c>
       <c r="E25">
-        <v>-37.09611452249518</v>
+        <v>-37.21453503700002</v>
       </c>
       <c r="F25">
-        <v>6.817747707811583</v>
+        <v>5.439521620177405</v>
       </c>
       <c r="G25">
-        <v>-7.382458067130664</v>
+        <v>-7.371487718358806</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.850089314740941</v>
       </c>
       <c r="E26">
-        <v>-40.19454307357967</v>
+        <v>-37.19692334437708</v>
       </c>
       <c r="F26">
-        <v>6.477923234691532</v>
+        <v>6.391236242723369</v>
       </c>
       <c r="G26">
-        <v>-6.562446687763302</v>
+        <v>-7.262799810286169</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.013560860867719</v>
       </c>
       <c r="E27">
-        <v>-39.25581763709663</v>
+        <v>-37.56525712053649</v>
       </c>
       <c r="F27">
-        <v>6.079939086220926</v>
+        <v>6.087727396542046</v>
       </c>
       <c r="G27">
-        <v>-8.68611118737406</v>
+        <v>-7.553219038601611</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.158630807200091</v>
       </c>
       <c r="E28">
-        <v>-41.45835282009102</v>
+        <v>-37.6245504420154</v>
       </c>
       <c r="F28">
-        <v>6.667944089954515</v>
+        <v>5.672695446921827</v>
       </c>
       <c r="G28">
-        <v>-7.693149727196101</v>
+        <v>-7.700833148527748</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.269436574002635</v>
       </c>
       <c r="E29">
-        <v>-39.65554969087174</v>
+        <v>-37.41156338224989</v>
       </c>
       <c r="F29">
-        <v>6.365802049987813</v>
+        <v>5.651283806294265</v>
       </c>
       <c r="G29">
-        <v>-7.369623646720751</v>
+        <v>-6.68054110859772</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.335914523098388</v>
       </c>
       <c r="E30">
-        <v>-39.67261108299413</v>
+        <v>-37.55500907159248</v>
       </c>
       <c r="F30">
-        <v>6.197766065595127</v>
+        <v>5.504463967822081</v>
       </c>
       <c r="G30">
-        <v>-6.096269522829522</v>
+        <v>-7.719186683003274</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.346544057010406</v>
       </c>
       <c r="E31">
-        <v>-41.05363691272612</v>
+        <v>-36.95322744007579</v>
       </c>
       <c r="F31">
-        <v>6.374072470137363</v>
+        <v>5.175552406866509</v>
       </c>
       <c r="G31">
-        <v>-5.760021283961677</v>
+        <v>-6.619950948127163</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.299404393660952</v>
       </c>
       <c r="E32">
-        <v>-37.6207274109909</v>
+        <v>-37.37150565902191</v>
       </c>
       <c r="F32">
-        <v>5.316159489817697</v>
+        <v>4.995251614707975</v>
       </c>
       <c r="G32">
-        <v>-8.753999684349074</v>
+        <v>-7.126657312093385</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.190016097744349</v>
       </c>
       <c r="E33">
-        <v>-37.64457515041806</v>
+        <v>-36.55473511988114</v>
       </c>
       <c r="F33">
-        <v>5.831962333988477</v>
+        <v>4.588615997082531</v>
       </c>
       <c r="G33">
-        <v>-6.306732087297529</v>
+        <v>-6.481693746815576</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.019157121043412</v>
       </c>
       <c r="E34">
-        <v>-38.11483080909443</v>
+        <v>-36.64032865207452</v>
       </c>
       <c r="F34">
-        <v>5.638959356075414</v>
+        <v>4.687204971894117</v>
       </c>
       <c r="G34">
-        <v>-5.034252562844322</v>
+        <v>-7.023595558614597</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.790726234129271</v>
       </c>
       <c r="E35">
-        <v>-38.16146721906092</v>
+        <v>-35.51956381001292</v>
       </c>
       <c r="F35">
-        <v>4.754228178454625</v>
+        <v>4.504821664084944</v>
       </c>
       <c r="G35">
-        <v>-5.267504316848156</v>
+        <v>-6.397340589076706</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.511303234764539</v>
       </c>
       <c r="E36">
-        <v>-38.47278778675875</v>
+        <v>-35.46284755616106</v>
       </c>
       <c r="F36">
-        <v>4.737329483437515</v>
+        <v>3.973299720078642</v>
       </c>
       <c r="G36">
-        <v>-6.239155574301153</v>
+        <v>-6.404394820961894</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.186076446254116</v>
       </c>
       <c r="E37">
-        <v>-36.28686129585234</v>
+        <v>-34.93056160974272</v>
       </c>
       <c r="F37">
-        <v>4.786117009992795</v>
+        <v>3.995846224048038</v>
       </c>
       <c r="G37">
-        <v>-7.015964352174772</v>
+        <v>-5.860370473810299</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.818071933821567</v>
       </c>
       <c r="E38">
-        <v>-38.19237749434596</v>
+        <v>-33.87110647325824</v>
       </c>
       <c r="F38">
-        <v>4.717891013963421</v>
+        <v>3.870502638860834</v>
       </c>
       <c r="G38">
-        <v>-5.32358572140986</v>
+        <v>-5.388042394619856</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.417105324072993</v>
       </c>
       <c r="E39">
-        <v>-39.30844090118786</v>
+        <v>-33.78235650045797</v>
       </c>
       <c r="F39">
-        <v>4.836115609690967</v>
+        <v>3.127425600588371</v>
       </c>
       <c r="G39">
-        <v>-5.289758303742806</v>
+        <v>-5.855631972377428</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.989330831556809</v>
       </c>
       <c r="E40">
-        <v>-35.62277318804057</v>
+        <v>-32.88662926082088</v>
       </c>
       <c r="F40">
-        <v>5.079460131406961</v>
+        <v>3.410329635992458</v>
       </c>
       <c r="G40">
-        <v>-6.287631879868944</v>
+        <v>-5.191904985723289</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.539766468985326</v>
       </c>
       <c r="E41">
-        <v>-35.47817290594968</v>
+        <v>-33.42086929316755</v>
       </c>
       <c r="F41">
-        <v>3.767773483770056</v>
+        <v>3.145571816914097</v>
       </c>
       <c r="G41">
-        <v>-3.730117760223867</v>
+        <v>-4.684420619868915</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.072394627480637</v>
       </c>
       <c r="E42">
-        <v>-34.16468452217639</v>
+        <v>-33.35328408527861</v>
       </c>
       <c r="F42">
-        <v>4.572121545357987</v>
+        <v>2.954649697916867</v>
       </c>
       <c r="G42">
-        <v>-4.619222495195043</v>
+        <v>-4.262811475850031</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.598111855974135</v>
       </c>
       <c r="E43">
-        <v>-34.1298266195271</v>
+        <v>-32.45734087865262</v>
       </c>
       <c r="F43">
-        <v>4.524493733166627</v>
+        <v>2.953765001530677</v>
       </c>
       <c r="G43">
-        <v>-4.607132136993597</v>
+        <v>-4.455938696233044</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.122323777850419</v>
       </c>
       <c r="E44">
-        <v>-34.93205053600267</v>
+        <v>-32.88607273050335</v>
       </c>
       <c r="F44">
-        <v>4.419170131370281</v>
+        <v>2.60749748675165</v>
       </c>
       <c r="G44">
-        <v>-4.066102313888009</v>
+        <v>-3.967920042050011</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.648321487006795</v>
       </c>
       <c r="E45">
-        <v>-34.33127398162659</v>
+        <v>-32.17966132268592</v>
       </c>
       <c r="F45">
-        <v>4.316739188544511</v>
+        <v>3.076596976752593</v>
       </c>
       <c r="G45">
-        <v>-4.14757320959829</v>
+        <v>-5.141065956300539</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.184307139516747</v>
       </c>
       <c r="E46">
-        <v>-35.04761364111603</v>
+        <v>-32.30483911201625</v>
       </c>
       <c r="F46">
-        <v>4.560693388668965</v>
+        <v>2.691623166710357</v>
       </c>
       <c r="G46">
-        <v>-4.724464220407411</v>
+        <v>-4.123363775004896</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.738280648515173</v>
       </c>
       <c r="E47">
-        <v>-34.97670586416723</v>
+        <v>-30.82835171998308</v>
       </c>
       <c r="F47">
-        <v>4.548120428229274</v>
+        <v>2.644205759839307</v>
       </c>
       <c r="G47">
-        <v>-3.702159296397634</v>
+        <v>-3.598470964216979</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.314272729509456</v>
       </c>
       <c r="E48">
-        <v>-32.28472926278143</v>
+        <v>-30.63406034099627</v>
       </c>
       <c r="F48">
-        <v>3.606278288389876</v>
+        <v>2.592898339644711</v>
       </c>
       <c r="G48">
-        <v>-4.577466246204777</v>
+        <v>-3.911039749643426</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.9145396829177992</v>
       </c>
       <c r="E49">
-        <v>-32.97118033697173</v>
+        <v>-29.77522815416329</v>
       </c>
       <c r="F49">
-        <v>4.026048499554109</v>
+        <v>2.437214969962572</v>
       </c>
       <c r="G49">
-        <v>-4.065397412848408</v>
+        <v>-4.249123341958824</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.5488212380240983</v>
       </c>
       <c r="E50">
-        <v>-31.977121666008</v>
+        <v>-30.48251796617593</v>
       </c>
       <c r="F50">
-        <v>3.755606423357737</v>
+        <v>2.410302969780422</v>
       </c>
       <c r="G50">
-        <v>-5.000774984952476</v>
+        <v>-4.241933351354898</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.2226414913446908</v>
       </c>
       <c r="E51">
-        <v>-32.23910208316686</v>
+        <v>-28.34495977435847</v>
       </c>
       <c r="F51">
-        <v>4.075864858423665</v>
+        <v>2.497816672416579</v>
       </c>
       <c r="G51">
-        <v>-4.785881986913351</v>
+        <v>-4.327819016168752</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.06007048974415231</v>
       </c>
       <c r="E52">
-        <v>-31.93230228599611</v>
+        <v>-28.98689257635795</v>
       </c>
       <c r="F52">
-        <v>3.779751676414537</v>
+        <v>2.594526909958615</v>
       </c>
       <c r="G52">
-        <v>-4.137119788255473</v>
+        <v>-3.848209570313694</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.2940383426799686</v>
       </c>
       <c r="E53">
-        <v>-30.37537757362933</v>
+        <v>-28.33806752016492</v>
       </c>
       <c r="F53">
-        <v>3.323737077908214</v>
+        <v>2.407741657770966</v>
       </c>
       <c r="G53">
-        <v>-5.280743402669692</v>
+        <v>-3.97328773292934</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.473432876313572</v>
       </c>
       <c r="E54">
-        <v>-29.55554196453082</v>
+        <v>-28.05680374282488</v>
       </c>
       <c r="F54">
-        <v>3.056881832565965</v>
+        <v>2.195668005510653</v>
       </c>
       <c r="G54">
-        <v>-3.670994838213515</v>
+        <v>-4.033342690758719</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.5964316152107738</v>
       </c>
       <c r="E55">
-        <v>-29.23171192432261</v>
+        <v>-26.78934540016467</v>
       </c>
       <c r="F55">
-        <v>3.733361445122959</v>
+        <v>1.795405846682349</v>
       </c>
       <c r="G55">
-        <v>-5.199071479625895</v>
+        <v>-4.463000760352006</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.6629511827900336</v>
       </c>
       <c r="E56">
-        <v>-26.98496165356409</v>
+        <v>-26.31822587353274</v>
       </c>
       <c r="F56">
-        <v>3.372226392198487</v>
+        <v>2.00499936693868</v>
       </c>
       <c r="G56">
-        <v>-5.0856998957568</v>
+        <v>-4.542568423255366</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.6715789883140326</v>
       </c>
       <c r="E57">
-        <v>-28.18935971207377</v>
+        <v>-26.16705728773163</v>
       </c>
       <c r="F57">
-        <v>3.432292969310284</v>
+        <v>1.718491933332415</v>
       </c>
       <c r="G57">
-        <v>-4.036668779367798</v>
+        <v>-4.4955828528491</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.6242856160498012</v>
       </c>
       <c r="E58">
-        <v>-27.99456994772799</v>
+        <v>-26.47872257196942</v>
       </c>
       <c r="F58">
-        <v>3.899815247776297</v>
+        <v>2.07271840211754</v>
       </c>
       <c r="G58">
-        <v>-5.657074403244899</v>
+        <v>-5.279304882399988</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.5237497966478336</v>
       </c>
       <c r="E59">
-        <v>-26.27568452993252</v>
+        <v>-25.38681424219272</v>
       </c>
       <c r="F59">
-        <v>2.827858126509569</v>
+        <v>1.476403216599065</v>
       </c>
       <c r="G59">
-        <v>-5.757548908833893</v>
+        <v>-5.446705825582172</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.3753346197306196</v>
       </c>
       <c r="E60">
-        <v>-26.42203954380816</v>
+        <v>-25.20482467515006</v>
       </c>
       <c r="F60">
-        <v>2.72052159192442</v>
+        <v>1.982351802146141</v>
       </c>
       <c r="G60">
-        <v>-5.056718020050852</v>
+        <v>-5.157461432332731</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.1869104557991897</v>
       </c>
       <c r="E61">
-        <v>-27.90964508255789</v>
+        <v>-24.76146936622461</v>
       </c>
       <c r="F61">
-        <v>2.941203638234625</v>
+        <v>1.179668759037837</v>
       </c>
       <c r="G61">
-        <v>-6.443185264096655</v>
+        <v>-5.469643827559693</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.03101787237168736</v>
       </c>
       <c r="E62">
-        <v>-28.06441034936631</v>
+        <v>-24.46898361188489</v>
       </c>
       <c r="F62">
-        <v>3.001518725567263</v>
+        <v>1.562556739959825</v>
       </c>
       <c r="G62">
-        <v>-6.277366432136686</v>
+        <v>-5.477442121653349</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.2687119444829065</v>
       </c>
       <c r="E63">
-        <v>-25.86067488829903</v>
+        <v>-23.30597645743845</v>
       </c>
       <c r="F63">
-        <v>2.71968991105201</v>
+        <v>0.6271841495362903</v>
       </c>
       <c r="G63">
-        <v>-6.704557348091371</v>
+        <v>-5.933293791729275</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.5157609777152028</v>
       </c>
       <c r="E64">
-        <v>-26.16733139967907</v>
+        <v>-23.54327849290518</v>
       </c>
       <c r="F64">
-        <v>3.281924404884507</v>
+        <v>0.6490679595834477</v>
       </c>
       <c r="G64">
-        <v>-5.531604628940585</v>
+        <v>-6.720835340616962</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.7602104263832606</v>
       </c>
       <c r="E65">
-        <v>-23.94572882349239</v>
+        <v>-23.34317261806361</v>
       </c>
       <c r="F65">
-        <v>2.683095952665938</v>
+        <v>0.9033684685688679</v>
       </c>
       <c r="G65">
-        <v>-7.401064843831529</v>
+        <v>-6.472182804270151</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.9910846899319226</v>
       </c>
       <c r="E66">
-        <v>-25.4994036479975</v>
+        <v>-23.51378653928757</v>
       </c>
       <c r="F66">
-        <v>2.324588481143146</v>
+        <v>0.6507304929608663</v>
       </c>
       <c r="G66">
-        <v>-7.100669960433443</v>
+        <v>-6.401120947244638</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.197392824899761</v>
       </c>
       <c r="E67">
-        <v>-26.22361156634182</v>
+        <v>-22.49958064018709</v>
       </c>
       <c r="F67">
-        <v>2.279512040552408</v>
+        <v>0.4355529480422639</v>
       </c>
       <c r="G67">
-        <v>-5.399524449331572</v>
+        <v>-6.074255724437255</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.367536994815439</v>
       </c>
       <c r="E68">
-        <v>-25.67655057063541</v>
+        <v>-23.4544413026671</v>
       </c>
       <c r="F68">
-        <v>1.767811271760292</v>
+        <v>0.5832210347349149</v>
       </c>
       <c r="G68">
-        <v>-6.687284661876565</v>
+        <v>-6.992733946803047</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.491722116852439</v>
       </c>
       <c r="E69">
-        <v>-23.30643331068418</v>
+        <v>-22.67328455063672</v>
       </c>
       <c r="F69">
-        <v>2.10784449346585</v>
+        <v>-0.365147811871141</v>
       </c>
       <c r="G69">
-        <v>-6.299978091040319</v>
+        <v>-6.715890590361393</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.561334328326743</v>
       </c>
       <c r="E70">
-        <v>-25.31281647601825</v>
+        <v>-22.6494949561681</v>
       </c>
       <c r="F70">
-        <v>1.750385735075002</v>
+        <v>0.0682573267431715</v>
       </c>
       <c r="G70">
-        <v>-6.060081992052101</v>
+        <v>-6.50904651789667</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.568975738548327</v>
       </c>
       <c r="E71">
-        <v>-24.28855565230036</v>
+        <v>-22.07369373809387</v>
       </c>
       <c r="F71">
-        <v>1.823489158372058</v>
+        <v>-0.3411690606623037</v>
       </c>
       <c r="G71">
-        <v>-6.142918307183534</v>
+        <v>-6.674465905934199</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.50963326493927</v>
       </c>
       <c r="E72">
-        <v>-25.61014902797405</v>
+        <v>-22.87905955893667</v>
       </c>
       <c r="F72">
-        <v>1.204690424806799</v>
+        <v>-0.1483069052077172</v>
       </c>
       <c r="G72">
-        <v>-6.94244056299984</v>
+        <v>-6.689143512025439</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.379853678563012</v>
       </c>
       <c r="E73">
-        <v>-26.29151241829145</v>
+        <v>-22.31657353636984</v>
       </c>
       <c r="F73">
-        <v>1.09596885992417</v>
+        <v>-0.261361659974391</v>
       </c>
       <c r="G73">
-        <v>-4.334729657101428</v>
+        <v>-6.074046864869966</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.177564440498547</v>
       </c>
       <c r="E74">
-        <v>-25.0457359153525</v>
+        <v>-23.47634118598291</v>
       </c>
       <c r="F74">
-        <v>0.8749422127744001</v>
+        <v>-0.3105028994106661</v>
       </c>
       <c r="G74">
-        <v>-5.522983950300729</v>
+        <v>-6.155298458034594</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.9049185452898757</v>
       </c>
       <c r="E75">
-        <v>-25.80354331331469</v>
+        <v>-23.02527751683859</v>
       </c>
       <c r="F75">
-        <v>1.611559642039832</v>
+        <v>-0.3763697050768659</v>
       </c>
       <c r="G75">
-        <v>-5.41143205541164</v>
+        <v>-5.793305666753781</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.5709691471775475</v>
       </c>
       <c r="E76">
-        <v>-25.14362295306739</v>
+        <v>-22.89308910679194</v>
       </c>
       <c r="F76">
-        <v>0.4816457954362368</v>
+        <v>-0.8064315528534797</v>
       </c>
       <c r="G76">
-        <v>-3.855203755073286</v>
+        <v>-5.362467540605311</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.1837096834350243</v>
       </c>
       <c r="E77">
-        <v>-24.11607693919155</v>
+        <v>-24.06849359704299</v>
       </c>
       <c r="F77">
-        <v>0.9654645458175244</v>
+        <v>-0.6862313008702574</v>
       </c>
       <c r="G77">
-        <v>-4.663051675390653</v>
+        <v>-5.172201696294157</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.2458183962364594</v>
       </c>
       <c r="E78">
-        <v>-25.59733221782563</v>
+        <v>-24.00552260693594</v>
       </c>
       <c r="F78">
-        <v>0.7805464337557853</v>
+        <v>-0.5325766029575743</v>
       </c>
       <c r="G78">
-        <v>-3.533546967725174</v>
+        <v>-5.280406616617438</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.7020537198840678</v>
       </c>
       <c r="E79">
-        <v>-26.86588493166994</v>
+        <v>-24.20748912045103</v>
       </c>
       <c r="F79">
-        <v>0.6846322572878388</v>
+        <v>-1.130693487577138</v>
       </c>
       <c r="G79">
-        <v>-3.395381142474277</v>
+        <v>-4.74509954565557</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.169209741052967</v>
       </c>
       <c r="E80">
-        <v>-26.82367999818702</v>
+        <v>-24.4075783824473</v>
       </c>
       <c r="F80">
-        <v>1.127513090622775</v>
+        <v>-1.291119260640304</v>
       </c>
       <c r="G80">
-        <v>-3.711471822354136</v>
+        <v>-4.531869591920984</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.634901519284578</v>
       </c>
       <c r="E81">
-        <v>-28.82429019977959</v>
+        <v>-25.53529570026667</v>
       </c>
       <c r="F81">
-        <v>1.057113458528456</v>
+        <v>-1.099995019996791</v>
       </c>
       <c r="G81">
-        <v>-3.119331452388322</v>
+        <v>-3.875888684468677</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.085515091976001</v>
       </c>
       <c r="E82">
-        <v>-27.32606074646094</v>
+        <v>-26.09168480860864</v>
       </c>
       <c r="F82">
-        <v>-0.2572471590846858</v>
+        <v>-1.026546167492767</v>
       </c>
       <c r="G82">
-        <v>-3.563847269449635</v>
+        <v>-3.370660001941025</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.50615241591204</v>
       </c>
       <c r="E83">
-        <v>-26.00931832161465</v>
+        <v>-27.32329055450728</v>
       </c>
       <c r="F83">
-        <v>-0.07270843929342875</v>
+        <v>-1.035881039754915</v>
       </c>
       <c r="G83">
-        <v>-2.681172798406371</v>
+        <v>-2.86153086699425</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.887344729744331</v>
       </c>
       <c r="E84">
-        <v>-30.43782525910945</v>
+        <v>-27.42531834391301</v>
       </c>
       <c r="F84">
-        <v>0.360369494196778</v>
+        <v>-1.040112340448414</v>
       </c>
       <c r="G84">
-        <v>-1.371028061737173</v>
+        <v>-3.54310490367324</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.221332152201889</v>
       </c>
       <c r="E85">
-        <v>-31.36004998699895</v>
+        <v>-29.2174414902105</v>
       </c>
       <c r="F85">
-        <v>0.6853902134614004</v>
+        <v>-0.9372092282030489</v>
       </c>
       <c r="G85">
-        <v>-2.06422774408039</v>
+        <v>-3.331258644571943</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.499305247490454</v>
       </c>
       <c r="E86">
-        <v>-30.67926181645004</v>
+        <v>-29.69131874916211</v>
       </c>
       <c r="F86">
-        <v>0.500005730551885</v>
+        <v>-1.048291640183657</v>
       </c>
       <c r="G86">
-        <v>-1.086783244379714</v>
+        <v>-2.678032072663262</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.713296707678376</v>
       </c>
       <c r="E87">
-        <v>-31.41200873727822</v>
+        <v>-32.09113147008587</v>
       </c>
       <c r="F87">
-        <v>0.3674271844686298</v>
+        <v>-0.9500240719243571</v>
       </c>
       <c r="G87">
-        <v>-2.148821090321643</v>
+        <v>-2.525854381191859</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.859469880729834</v>
       </c>
       <c r="E88">
-        <v>-31.47410962961272</v>
+        <v>-32.19153743046926</v>
       </c>
       <c r="F88">
-        <v>-0.4534492919073599</v>
+        <v>-0.862049797012244</v>
       </c>
       <c r="G88">
-        <v>-2.653718208286223</v>
+        <v>-3.304059907421725</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.93374561047547</v>
       </c>
       <c r="E89">
-        <v>-33.30538717567503</v>
+        <v>-33.52519796164724</v>
       </c>
       <c r="F89">
-        <v>-0.2700644879082026</v>
+        <v>-0.638322672129348</v>
       </c>
       <c r="G89">
-        <v>-3.009831602747849</v>
+        <v>-2.41277520071697</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.933305889665316</v>
       </c>
       <c r="E90">
-        <v>-38.1103681835259</v>
+        <v>-35.74412586974073</v>
       </c>
       <c r="F90">
-        <v>0.08722362679766898</v>
+        <v>-0.8287485990523011</v>
       </c>
       <c r="G90">
-        <v>-1.644064952564982</v>
+        <v>-2.479500610976643</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.8576072184878</v>
       </c>
       <c r="E91">
-        <v>-36.28526230949228</v>
+        <v>-36.3507210731829</v>
       </c>
       <c r="F91">
-        <v>0.04366227018665139</v>
+        <v>-0.5205768727606207</v>
       </c>
       <c r="G91">
-        <v>-2.463233061429416</v>
+        <v>-3.185861056803662</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.706472792714246</v>
       </c>
       <c r="E92">
-        <v>-38.38708211785959</v>
+        <v>-38.32111458578167</v>
       </c>
       <c r="F92">
-        <v>0.02852137079828202</v>
+        <v>-0.796096841136153</v>
       </c>
       <c r="G92">
-        <v>-2.158245878295562</v>
+        <v>-2.703207482755367</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.482082558295483</v>
       </c>
       <c r="E93">
-        <v>-40.94267556576067</v>
+        <v>-40.35994263798531</v>
       </c>
       <c r="F93">
-        <v>0.1809509133222247</v>
+        <v>-0.5297634672576672</v>
       </c>
       <c r="G93">
-        <v>-3.855310795601522</v>
+        <v>-3.089305278845929</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.188767729070839</v>
       </c>
       <c r="E94">
-        <v>-41.22735328280972</v>
+        <v>-41.19347969124442</v>
       </c>
       <c r="F94">
-        <v>0.5389439686878786</v>
+        <v>-0.4059656156440867</v>
       </c>
       <c r="G94">
-        <v>-2.102394219257875</v>
+        <v>-3.308633931945355</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.832487378055946</v>
       </c>
       <c r="E95">
-        <v>-42.0234823616661</v>
+        <v>-43.11643730069666</v>
       </c>
       <c r="F95">
-        <v>-0.8930580740012379</v>
+        <v>-0.107776544923543</v>
       </c>
       <c r="G95">
-        <v>-4.509372805779361</v>
+        <v>-4.304914953870915</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.41576885228061</v>
       </c>
       <c r="E96">
-        <v>-46.62106757049751</v>
+        <v>-45.34819032536122</v>
       </c>
       <c r="F96">
-        <v>-0.807938353159172</v>
+        <v>-0.2571833747946702</v>
       </c>
       <c r="G96">
-        <v>-2.814033590648126</v>
+        <v>-3.912645357566961</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.955882160873492</v>
       </c>
       <c r="E97">
-        <v>-47.96433447946981</v>
+        <v>-46.31298235442173</v>
       </c>
       <c r="F97">
-        <v>-0.1038931585392189</v>
+        <v>0.1894756422644344</v>
       </c>
       <c r="G97">
-        <v>-3.90598273737044</v>
+        <v>-4.771139112207334</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.453767319785737</v>
       </c>
       <c r="E98">
-        <v>-48.7999336021517</v>
+        <v>-48.59962318165239</v>
       </c>
       <c r="F98">
-        <v>0.8904045187150557</v>
+        <v>0.1142126651482797</v>
       </c>
       <c r="G98">
-        <v>-4.091238562811247</v>
+        <v>-5.400117088353755</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.9346125297506642</v>
       </c>
       <c r="E99">
-        <v>-51.42622093661836</v>
+        <v>-50.61075450583358</v>
       </c>
       <c r="F99">
-        <v>1.106275407149801</v>
+        <v>0.2084311735426954</v>
       </c>
       <c r="G99">
-        <v>-5.198982714309797</v>
+        <v>-4.908652251310452</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.3876642039812207</v>
       </c>
       <c r="E100">
-        <v>-52.26424034319979</v>
+        <v>-52.26176814415869</v>
       </c>
       <c r="F100">
-        <v>0.6894724080223964</v>
+        <v>0.3565532055720806</v>
       </c>
       <c r="G100">
-        <v>-4.056270249757876</v>
+        <v>-5.694452433555868</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.1341287510212523</v>
       </c>
       <c r="E101">
-        <v>-53.50033155732924</v>
+        <v>-55.32275030363569</v>
       </c>
       <c r="F101">
-        <v>1.34370041540539</v>
+        <v>0.8887626945227071</v>
       </c>
       <c r="G101">
-        <v>-5.863879314540755</v>
+        <v>-5.903823706784788</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.6827576831244035</v>
       </c>
       <c r="E102">
-        <v>-54.91824984410826</v>
+        <v>-56.67188570020998</v>
       </c>
       <c r="F102">
-        <v>1.063586321413931</v>
+        <v>1.145248436716712</v>
       </c>
       <c r="G102">
-        <v>-4.81793670900304</v>
+        <v>-6.49087051405334</v>
       </c>
     </row>
   </sheetData>
